--- a/medical_data/results/TN3K_Thyroid_Ultrasound/tn3k_final_results.xlsx
+++ b/medical_data/results/TN3K_Thyroid_Ultrasound/tn3k_final_results.xlsx
@@ -506,19 +506,19 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9369</v>
+        <v>0.8596</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1246</v>
+        <v>0.8829</v>
       </c>
       <c r="F2" t="n">
-        <v>0.098</v>
+        <v>0.8977000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9477</v>
+        <v>0.9851</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5544</v>
+        <v>0.9939</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
         <v>50</v>
@@ -552,19 +552,19 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9222</v>
+        <v>0.8342000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1499</v>
+        <v>0.8468</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1349</v>
+        <v>0.9436</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9268</v>
+        <v>0.9686</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6089</v>
+        <v>0.9935</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
         <v>50</v>
@@ -598,19 +598,19 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9387</v>
+        <v>0.8645</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1469</v>
+        <v>0.8779</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1264</v>
+        <v>0.8929</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9346</v>
+        <v>0.9844000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6011</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -618,7 +618,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="K4" t="n">
         <v>50</v>
@@ -632,7 +632,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -641,22 +641,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.6788</v>
+        <v>6.8957</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9361</v>
+        <v>0.8559</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1228</v>
+        <v>0.8774999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0994</v>
+        <v>0.8868</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9427</v>
+        <v>0.9852</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5947</v>
+        <v>0.9936</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="K5" t="n">
         <v>50</v>
@@ -690,19 +690,19 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9381</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1231</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1006</v>
+        <v>0.8986</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9412</v>
+        <v>0.983</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5773</v>
+        <v>0.9937</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="K6" t="n">
         <v>50</v>
@@ -724,7 +724,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -733,22 +733,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>4.8046</v>
+        <v>9.264099999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9349</v>
+        <v>0.8512</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1212</v>
+        <v>0.8646</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0968</v>
+        <v>0.9164</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9448</v>
+        <v>0.9776</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5871</v>
+        <v>0.9933</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -756,7 +756,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>10.4</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
         <v>50</v>
@@ -813,10 +813,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.467826</v>
+        <v>0.595044</v>
       </c>
       <c r="D2" t="n">
-        <v>0.775138</v>
+        <v>0.531913</v>
       </c>
     </row>
     <row r="3">
@@ -829,10 +829,10 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>0.226921</v>
+        <v>0.471392</v>
       </c>
       <c r="D3" t="n">
-        <v>0.853747</v>
+        <v>0.741051</v>
       </c>
     </row>
     <row r="4">
@@ -845,10 +845,10 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>0.161935</v>
+        <v>0.430258</v>
       </c>
       <c r="D4" t="n">
-        <v>0.844791</v>
+        <v>0.713593</v>
       </c>
     </row>
     <row r="5">
@@ -861,10 +861,10 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>0.135167</v>
+        <v>0.42311</v>
       </c>
       <c r="D5" t="n">
-        <v>0.858828</v>
+        <v>0.720191</v>
       </c>
     </row>
     <row r="6">
@@ -877,10 +877,10 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>0.12434</v>
+        <v>0.386145</v>
       </c>
       <c r="D6" t="n">
-        <v>0.867671</v>
+        <v>0.792431</v>
       </c>
     </row>
     <row r="7">
@@ -893,10 +893,10 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>0.113042</v>
+        <v>0.363425</v>
       </c>
       <c r="D7" t="n">
-        <v>0.888007</v>
+        <v>0.7444539999999999</v>
       </c>
     </row>
     <row r="8">
@@ -909,10 +909,10 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>0.105572</v>
+        <v>0.374234</v>
       </c>
       <c r="D8" t="n">
-        <v>0.894346</v>
+        <v>0.801967</v>
       </c>
     </row>
     <row r="9">
@@ -925,10 +925,10 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>0.100529</v>
+        <v>0.355941</v>
       </c>
       <c r="D9" t="n">
-        <v>0.894779</v>
+        <v>0.804162</v>
       </c>
     </row>
     <row r="10">
@@ -941,10 +941,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>0.096263</v>
+        <v>0.345189</v>
       </c>
       <c r="D10" t="n">
-        <v>0.900119</v>
+        <v>0.809624</v>
       </c>
     </row>
     <row r="11">
@@ -957,10 +957,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>0.090138</v>
+        <v>0.340207</v>
       </c>
       <c r="D11" t="n">
-        <v>0.902918</v>
+        <v>0.821557</v>
       </c>
     </row>
     <row r="12">
@@ -973,10 +973,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>0.091298</v>
+        <v>0.337952</v>
       </c>
       <c r="D12" t="n">
-        <v>0.90633</v>
+        <v>0.80686</v>
       </c>
     </row>
     <row r="13">
@@ -989,10 +989,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>0.086566</v>
+        <v>0.333517</v>
       </c>
       <c r="D13" t="n">
-        <v>0.910627</v>
+        <v>0.830291</v>
       </c>
     </row>
     <row r="14">
@@ -1005,10 +1005,10 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>0.08645600000000001</v>
+        <v>0.320554</v>
       </c>
       <c r="D14" t="n">
-        <v>0.894795</v>
+        <v>0.828725</v>
       </c>
     </row>
     <row r="15">
@@ -1021,10 +1021,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>0.082178</v>
+        <v>0.325156</v>
       </c>
       <c r="D15" t="n">
-        <v>0.913664</v>
+        <v>0.821002</v>
       </c>
     </row>
     <row r="16">
@@ -1037,10 +1037,10 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>0.08004799999999999</v>
+        <v>0.320853</v>
       </c>
       <c r="D16" t="n">
-        <v>0.907772</v>
+        <v>0.830205</v>
       </c>
     </row>
     <row r="17">
@@ -1053,10 +1053,10 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>0.078488</v>
+        <v>0.309484</v>
       </c>
       <c r="D17" t="n">
-        <v>0.909122</v>
+        <v>0.802244</v>
       </c>
     </row>
     <row r="18">
@@ -1069,10 +1069,10 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>0.076002</v>
+        <v>0.312494</v>
       </c>
       <c r="D18" t="n">
-        <v>0.914488</v>
+        <v>0.825394</v>
       </c>
     </row>
     <row r="19">
@@ -1085,10 +1085,10 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>0.07546600000000001</v>
+        <v>0.310526</v>
       </c>
       <c r="D19" t="n">
-        <v>0.918295</v>
+        <v>0.815317</v>
       </c>
     </row>
     <row r="20">
@@ -1101,10 +1101,10 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>0.07391300000000001</v>
+        <v>0.303953</v>
       </c>
       <c r="D20" t="n">
-        <v>0.916675</v>
+        <v>0.843456</v>
       </c>
     </row>
     <row r="21">
@@ -1117,10 +1117,10 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>0.072061</v>
+        <v>0.292569</v>
       </c>
       <c r="D21" t="n">
-        <v>0.921314</v>
+        <v>0.836839</v>
       </c>
     </row>
     <row r="22">
@@ -1133,10 +1133,10 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>0.070642</v>
+        <v>0.294486</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9215410000000001</v>
+        <v>0.839624</v>
       </c>
     </row>
     <row r="23">
@@ -1149,10 +1149,10 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>0.07081999999999999</v>
+        <v>0.300851</v>
       </c>
       <c r="D23" t="n">
-        <v>0.925</v>
+        <v>0.845471</v>
       </c>
     </row>
     <row r="24">
@@ -1165,10 +1165,10 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>0.068594</v>
+        <v>0.293899</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9258459999999999</v>
+        <v>0.829218</v>
       </c>
     </row>
     <row r="25">
@@ -1181,10 +1181,10 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>0.064857</v>
+        <v>0.282625</v>
       </c>
       <c r="D25" t="n">
-        <v>0.91686</v>
+        <v>0.845122</v>
       </c>
     </row>
     <row r="26">
@@ -1197,10 +1197,10 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>0.06537800000000001</v>
+        <v>0.279033</v>
       </c>
       <c r="D26" t="n">
-        <v>0.91417</v>
+        <v>0.8486359999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1213,10 +1213,10 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>0.063177</v>
+        <v>0.271657</v>
       </c>
       <c r="D27" t="n">
-        <v>0.927121</v>
+        <v>0.849676</v>
       </c>
     </row>
     <row r="28">
@@ -1229,10 +1229,10 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>0.063814</v>
+        <v>0.2744</v>
       </c>
       <c r="D28" t="n">
-        <v>0.92531</v>
+        <v>0.849777</v>
       </c>
     </row>
     <row r="29">
@@ -1245,10 +1245,10 @@
         <v>28</v>
       </c>
       <c r="C29" t="n">
-        <v>0.061639</v>
+        <v>0.278333</v>
       </c>
       <c r="D29" t="n">
-        <v>0.929002</v>
+        <v>0.853506</v>
       </c>
     </row>
     <row r="30">
@@ -1261,10 +1261,10 @@
         <v>29</v>
       </c>
       <c r="C30" t="n">
-        <v>0.059851</v>
+        <v>0.268669</v>
       </c>
       <c r="D30" t="n">
-        <v>0.931909</v>
+        <v>0.843646</v>
       </c>
     </row>
     <row r="31">
@@ -1277,10 +1277,10 @@
         <v>30</v>
       </c>
       <c r="C31" t="n">
-        <v>0.059454</v>
+        <v>0.273507</v>
       </c>
       <c r="D31" t="n">
-        <v>0.927775</v>
+        <v>0.852992</v>
       </c>
     </row>
     <row r="32">
@@ -1293,10 +1293,10 @@
         <v>31</v>
       </c>
       <c r="C32" t="n">
-        <v>0.059339</v>
+        <v>0.275603</v>
       </c>
       <c r="D32" t="n">
-        <v>0.93289</v>
+        <v>0.855005</v>
       </c>
     </row>
     <row r="33">
@@ -1309,10 +1309,10 @@
         <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>0.057157</v>
+        <v>0.257759</v>
       </c>
       <c r="D33" t="n">
-        <v>0.931269</v>
+        <v>0.850538</v>
       </c>
     </row>
     <row r="34">
@@ -1325,10 +1325,10 @@
         <v>33</v>
       </c>
       <c r="C34" t="n">
-        <v>0.057296</v>
+        <v>0.255431</v>
       </c>
       <c r="D34" t="n">
-        <v>0.93044</v>
+        <v>0.855473</v>
       </c>
     </row>
     <row r="35">
@@ -1341,10 +1341,10 @@
         <v>34</v>
       </c>
       <c r="C35" t="n">
-        <v>0.056132</v>
+        <v>0.253522</v>
       </c>
       <c r="D35" t="n">
-        <v>0.932073</v>
+        <v>0.854247</v>
       </c>
     </row>
     <row r="36">
@@ -1357,10 +1357,10 @@
         <v>35</v>
       </c>
       <c r="C36" t="n">
-        <v>0.055482</v>
+        <v>0.246682</v>
       </c>
       <c r="D36" t="n">
-        <v>0.932235</v>
+        <v>0.851811</v>
       </c>
     </row>
     <row r="37">
@@ -1373,10 +1373,10 @@
         <v>36</v>
       </c>
       <c r="C37" t="n">
-        <v>0.054929</v>
+        <v>0.249648</v>
       </c>
       <c r="D37" t="n">
-        <v>0.9341739999999999</v>
+        <v>0.8554310000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1389,10 +1389,10 @@
         <v>37</v>
       </c>
       <c r="C38" t="n">
-        <v>0.053883</v>
+        <v>0.2444</v>
       </c>
       <c r="D38" t="n">
-        <v>0.93542</v>
+        <v>0.856939</v>
       </c>
     </row>
     <row r="39">
@@ -1405,10 +1405,10 @@
         <v>38</v>
       </c>
       <c r="C39" t="n">
-        <v>0.053386</v>
+        <v>0.248127</v>
       </c>
       <c r="D39" t="n">
-        <v>0.935852</v>
+        <v>0.857549</v>
       </c>
     </row>
     <row r="40">
@@ -1421,10 +1421,10 @@
         <v>39</v>
       </c>
       <c r="C40" t="n">
-        <v>0.053036</v>
+        <v>0.249764</v>
       </c>
       <c r="D40" t="n">
-        <v>0.934437</v>
+        <v>0.859426</v>
       </c>
     </row>
     <row r="41">
@@ -1437,10 +1437,10 @@
         <v>40</v>
       </c>
       <c r="C41" t="n">
-        <v>0.053279</v>
+        <v>0.248712</v>
       </c>
       <c r="D41" t="n">
-        <v>0.934916</v>
+        <v>0.855903</v>
       </c>
     </row>
     <row r="42">
@@ -1453,10 +1453,10 @@
         <v>41</v>
       </c>
       <c r="C42" t="n">
-        <v>0.051243</v>
+        <v>0.243649</v>
       </c>
       <c r="D42" t="n">
-        <v>0.936845</v>
+        <v>0.853604</v>
       </c>
     </row>
     <row r="43">
@@ -1469,10 +1469,10 @@
         <v>42</v>
       </c>
       <c r="C43" t="n">
-        <v>0.050908</v>
+        <v>0.23566</v>
       </c>
       <c r="D43" t="n">
-        <v>0.936262</v>
+        <v>0.856955</v>
       </c>
     </row>
     <row r="44">
@@ -1485,10 +1485,10 @@
         <v>43</v>
       </c>
       <c r="C44" t="n">
-        <v>0.051083</v>
+        <v>0.238731</v>
       </c>
       <c r="D44" t="n">
-        <v>0.9368840000000001</v>
+        <v>0.858515</v>
       </c>
     </row>
     <row r="45">
@@ -1501,10 +1501,10 @@
         <v>44</v>
       </c>
       <c r="C45" t="n">
-        <v>0.050843</v>
+        <v>0.233173</v>
       </c>
       <c r="D45" t="n">
-        <v>0.936492</v>
+        <v>0.858688</v>
       </c>
     </row>
     <row r="46">
@@ -1517,10 +1517,10 @@
         <v>45</v>
       </c>
       <c r="C46" t="n">
-        <v>0.049901</v>
+        <v>0.23686</v>
       </c>
       <c r="D46" t="n">
-        <v>0.936772</v>
+        <v>0.857945</v>
       </c>
     </row>
     <row r="47">
@@ -1533,10 +1533,10 @@
         <v>46</v>
       </c>
       <c r="C47" t="n">
-        <v>0.049703</v>
+        <v>0.236498</v>
       </c>
       <c r="D47" t="n">
-        <v>0.936389</v>
+        <v>0.859579</v>
       </c>
     </row>
     <row r="48">
@@ -1549,10 +1549,10 @@
         <v>47</v>
       </c>
       <c r="C48" t="n">
-        <v>0.049839</v>
+        <v>0.232454</v>
       </c>
       <c r="D48" t="n">
-        <v>0.9358</v>
+        <v>0.859281</v>
       </c>
     </row>
     <row r="49">
@@ -1565,10 +1565,10 @@
         <v>48</v>
       </c>
       <c r="C49" t="n">
-        <v>0.04918</v>
+        <v>0.226481</v>
       </c>
       <c r="D49" t="n">
-        <v>0.936364</v>
+        <v>0.858526</v>
       </c>
     </row>
     <row r="50">
@@ -1581,10 +1581,10 @@
         <v>49</v>
       </c>
       <c r="C50" t="n">
-        <v>0.049392</v>
+        <v>0.2333</v>
       </c>
       <c r="D50" t="n">
-        <v>0.93668</v>
+        <v>0.859387</v>
       </c>
     </row>
     <row r="51">
@@ -1597,10 +1597,10 @@
         <v>50</v>
       </c>
       <c r="C51" t="n">
-        <v>0.04998</v>
+        <v>0.227808</v>
       </c>
       <c r="D51" t="n">
-        <v>0.936947</v>
+        <v>0.85926</v>
       </c>
     </row>
     <row r="52">
@@ -1613,10 +1613,10 @@
         <v>1</v>
       </c>
       <c r="C52" t="n">
-        <v>0.464691</v>
+        <v>0.661367</v>
       </c>
       <c r="D52" t="n">
-        <v>0.744337</v>
+        <v>0.505145</v>
       </c>
     </row>
     <row r="53">
@@ -1629,10 +1629,10 @@
         <v>2</v>
       </c>
       <c r="C53" t="n">
-        <v>0.269937</v>
+        <v>0.55378</v>
       </c>
       <c r="D53" t="n">
-        <v>0.726291</v>
+        <v>0.71772</v>
       </c>
     </row>
     <row r="54">
@@ -1645,10 +1645,10 @@
         <v>3</v>
       </c>
       <c r="C54" t="n">
-        <v>0.204118</v>
+        <v>0.490745</v>
       </c>
       <c r="D54" t="n">
-        <v>0.84646</v>
+        <v>0.683001</v>
       </c>
     </row>
     <row r="55">
@@ -1661,10 +1661,10 @@
         <v>4</v>
       </c>
       <c r="C55" t="n">
-        <v>0.176355</v>
+        <v>0.4778</v>
       </c>
       <c r="D55" t="n">
-        <v>0.842624</v>
+        <v>0.734592</v>
       </c>
     </row>
     <row r="56">
@@ -1677,10 +1677,10 @@
         <v>5</v>
       </c>
       <c r="C56" t="n">
-        <v>0.161956</v>
+        <v>0.456275</v>
       </c>
       <c r="D56" t="n">
-        <v>0.85423</v>
+        <v>0.683981</v>
       </c>
     </row>
     <row r="57">
@@ -1693,10 +1693,10 @@
         <v>6</v>
       </c>
       <c r="C57" t="n">
-        <v>0.149596</v>
+        <v>0.439265</v>
       </c>
       <c r="D57" t="n">
-        <v>0.852317</v>
+        <v>0.628221</v>
       </c>
     </row>
     <row r="58">
@@ -1709,10 +1709,10 @@
         <v>7</v>
       </c>
       <c r="C58" t="n">
-        <v>0.139616</v>
+        <v>0.436131</v>
       </c>
       <c r="D58" t="n">
-        <v>0.8417249999999999</v>
+        <v>0.733428</v>
       </c>
     </row>
     <row r="59">
@@ -1725,10 +1725,10 @@
         <v>8</v>
       </c>
       <c r="C59" t="n">
-        <v>0.133764</v>
+        <v>0.42756</v>
       </c>
       <c r="D59" t="n">
-        <v>0.854607</v>
+        <v>0.785762</v>
       </c>
     </row>
     <row r="60">
@@ -1741,10 +1741,10 @@
         <v>9</v>
       </c>
       <c r="C60" t="n">
-        <v>0.129322</v>
+        <v>0.416963</v>
       </c>
       <c r="D60" t="n">
-        <v>0.857741</v>
+        <v>0.691852</v>
       </c>
     </row>
     <row r="61">
@@ -1757,10 +1757,10 @@
         <v>10</v>
       </c>
       <c r="C61" t="n">
-        <v>0.122711</v>
+        <v>0.406465</v>
       </c>
       <c r="D61" t="n">
-        <v>0.862554</v>
+        <v>0.789758</v>
       </c>
     </row>
     <row r="62">
@@ -1773,10 +1773,10 @@
         <v>11</v>
       </c>
       <c r="C62" t="n">
-        <v>0.119487</v>
+        <v>0.403404</v>
       </c>
       <c r="D62" t="n">
-        <v>0.875932</v>
+        <v>0.6987449999999999</v>
       </c>
     </row>
     <row r="63">
@@ -1789,10 +1789,10 @@
         <v>12</v>
       </c>
       <c r="C63" t="n">
-        <v>0.118893</v>
+        <v>0.398182</v>
       </c>
       <c r="D63" t="n">
-        <v>0.890225</v>
+        <v>0.7875</v>
       </c>
     </row>
     <row r="64">
@@ -1805,10 +1805,10 @@
         <v>13</v>
       </c>
       <c r="C64" t="n">
-        <v>0.114819</v>
+        <v>0.385883</v>
       </c>
       <c r="D64" t="n">
-        <v>0.8932600000000001</v>
+        <v>0.794106</v>
       </c>
     </row>
     <row r="65">
@@ -1821,10 +1821,10 @@
         <v>14</v>
       </c>
       <c r="C65" t="n">
-        <v>0.110708</v>
+        <v>0.380411</v>
       </c>
       <c r="D65" t="n">
-        <v>0.873704</v>
+        <v>0.7984869999999999</v>
       </c>
     </row>
     <row r="66">
@@ -1837,10 +1837,10 @@
         <v>15</v>
       </c>
       <c r="C66" t="n">
-        <v>0.107967</v>
+        <v>0.363667</v>
       </c>
       <c r="D66" t="n">
-        <v>0.881314</v>
+        <v>0.764505</v>
       </c>
     </row>
     <row r="67">
@@ -1853,10 +1853,10 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>0.103987</v>
+        <v>0.377073</v>
       </c>
       <c r="D67" t="n">
-        <v>0.883468</v>
+        <v>0.777471</v>
       </c>
     </row>
     <row r="68">
@@ -1869,10 +1869,10 @@
         <v>17</v>
       </c>
       <c r="C68" t="n">
-        <v>0.102937</v>
+        <v>0.371324</v>
       </c>
       <c r="D68" t="n">
-        <v>0.892974</v>
+        <v>0.763405</v>
       </c>
     </row>
     <row r="69">
@@ -1885,10 +1885,10 @@
         <v>18</v>
       </c>
       <c r="C69" t="n">
-        <v>0.100151</v>
+        <v>0.361709</v>
       </c>
       <c r="D69" t="n">
-        <v>0.891269</v>
+        <v>0.804494</v>
       </c>
     </row>
     <row r="70">
@@ -1901,10 +1901,10 @@
         <v>19</v>
       </c>
       <c r="C70" t="n">
-        <v>0.098941</v>
+        <v>0.361534</v>
       </c>
       <c r="D70" t="n">
-        <v>0.896802</v>
+        <v>0.792061</v>
       </c>
     </row>
     <row r="71">
@@ -1917,10 +1917,10 @@
         <v>20</v>
       </c>
       <c r="C71" t="n">
-        <v>0.095801</v>
+        <v>0.349665</v>
       </c>
       <c r="D71" t="n">
-        <v>0.895187</v>
+        <v>0.809603</v>
       </c>
     </row>
     <row r="72">
@@ -1933,10 +1933,10 @@
         <v>21</v>
       </c>
       <c r="C72" t="n">
-        <v>0.095209</v>
+        <v>0.354197</v>
       </c>
       <c r="D72" t="n">
-        <v>0.900448</v>
+        <v>0.763475</v>
       </c>
     </row>
     <row r="73">
@@ -1949,10 +1949,10 @@
         <v>22</v>
       </c>
       <c r="C73" t="n">
-        <v>0.092972</v>
+        <v>0.360727</v>
       </c>
       <c r="D73" t="n">
-        <v>0.912479</v>
+        <v>0.79673</v>
       </c>
     </row>
     <row r="74">
@@ -1965,10 +1965,10 @@
         <v>23</v>
       </c>
       <c r="C74" t="n">
-        <v>0.09111</v>
+        <v>0.344679</v>
       </c>
       <c r="D74" t="n">
-        <v>0.895863</v>
+        <v>0.813829</v>
       </c>
     </row>
     <row r="75">
@@ -1981,10 +1981,10 @@
         <v>24</v>
       </c>
       <c r="C75" t="n">
-        <v>0.08980399999999999</v>
+        <v>0.34253</v>
       </c>
       <c r="D75" t="n">
-        <v>0.910942</v>
+        <v>0.832026</v>
       </c>
     </row>
     <row r="76">
@@ -1997,10 +1997,10 @@
         <v>25</v>
       </c>
       <c r="C76" t="n">
-        <v>0.08703</v>
+        <v>0.335243</v>
       </c>
       <c r="D76" t="n">
-        <v>0.903452</v>
+        <v>0.822784</v>
       </c>
     </row>
     <row r="77">
@@ -2013,10 +2013,10 @@
         <v>26</v>
       </c>
       <c r="C77" t="n">
-        <v>0.088533</v>
+        <v>0.340042</v>
       </c>
       <c r="D77" t="n">
-        <v>0.89142</v>
+        <v>0.827604</v>
       </c>
     </row>
     <row r="78">
@@ -2029,10 +2029,10 @@
         <v>27</v>
       </c>
       <c r="C78" t="n">
-        <v>0.08343399999999999</v>
+        <v>0.324906</v>
       </c>
       <c r="D78" t="n">
-        <v>0.90911</v>
+        <v>0.796006</v>
       </c>
     </row>
     <row r="79">
@@ -2045,10 +2045,10 @@
         <v>28</v>
       </c>
       <c r="C79" t="n">
-        <v>0.082201</v>
+        <v>0.318618</v>
       </c>
       <c r="D79" t="n">
-        <v>0.912285</v>
+        <v>0.791211</v>
       </c>
     </row>
     <row r="80">
@@ -2061,10 +2061,10 @@
         <v>29</v>
       </c>
       <c r="C80" t="n">
-        <v>0.081873</v>
+        <v>0.330424</v>
       </c>
       <c r="D80" t="n">
-        <v>0.905385</v>
+        <v>0.812369</v>
       </c>
     </row>
     <row r="81">
@@ -2077,10 +2077,10 @@
         <v>30</v>
       </c>
       <c r="C81" t="n">
-        <v>0.08183600000000001</v>
+        <v>0.333536</v>
       </c>
       <c r="D81" t="n">
-        <v>0.915766</v>
+        <v>0.823384</v>
       </c>
     </row>
     <row r="82">
@@ -2093,10 +2093,10 @@
         <v>31</v>
       </c>
       <c r="C82" t="n">
-        <v>0.07818899999999999</v>
+        <v>0.314283</v>
       </c>
       <c r="D82" t="n">
-        <v>0.922085</v>
+        <v>0.815461</v>
       </c>
     </row>
     <row r="83">
@@ -2109,10 +2109,10 @@
         <v>32</v>
       </c>
       <c r="C83" t="n">
-        <v>0.079869</v>
+        <v>0.318537</v>
       </c>
       <c r="D83" t="n">
-        <v>0.917946</v>
+        <v>0.812507</v>
       </c>
     </row>
     <row r="84">
@@ -2125,10 +2125,10 @@
         <v>33</v>
       </c>
       <c r="C84" t="n">
-        <v>0.077241</v>
+        <v>0.307395</v>
       </c>
       <c r="D84" t="n">
-        <v>0.913124</v>
+        <v>0.814414</v>
       </c>
     </row>
     <row r="85">
@@ -2141,10 +2141,10 @@
         <v>34</v>
       </c>
       <c r="C85" t="n">
-        <v>0.07477</v>
+        <v>0.317377</v>
       </c>
       <c r="D85" t="n">
-        <v>0.917736</v>
+        <v>0.815259</v>
       </c>
     </row>
     <row r="86">
@@ -2157,10 +2157,10 @@
         <v>35</v>
       </c>
       <c r="C86" t="n">
-        <v>0.07448100000000001</v>
+        <v>0.307419</v>
       </c>
       <c r="D86" t="n">
-        <v>0.911153</v>
+        <v>0.814458</v>
       </c>
     </row>
     <row r="87">
@@ -2173,10 +2173,10 @@
         <v>36</v>
       </c>
       <c r="C87" t="n">
-        <v>0.073728</v>
+        <v>0.30502</v>
       </c>
       <c r="D87" t="n">
-        <v>0.921883</v>
+        <v>0.83418</v>
       </c>
     </row>
     <row r="88">
@@ -2189,10 +2189,10 @@
         <v>37</v>
       </c>
       <c r="C88" t="n">
-        <v>0.072418</v>
+        <v>0.300729</v>
       </c>
       <c r="D88" t="n">
-        <v>0.913559</v>
+        <v>0.817867</v>
       </c>
     </row>
     <row r="89">
@@ -2205,10 +2205,10 @@
         <v>38</v>
       </c>
       <c r="C89" t="n">
-        <v>0.071867</v>
+        <v>0.29562</v>
       </c>
       <c r="D89" t="n">
-        <v>0.915045</v>
+        <v>0.812117</v>
       </c>
     </row>
     <row r="90">
@@ -2221,10 +2221,10 @@
         <v>39</v>
       </c>
       <c r="C90" t="n">
-        <v>0.07055400000000001</v>
+        <v>0.299133</v>
       </c>
       <c r="D90" t="n">
-        <v>0.919522</v>
+        <v>0.816512</v>
       </c>
     </row>
     <row r="91">
@@ -2237,10 +2237,10 @@
         <v>40</v>
       </c>
       <c r="C91" t="n">
-        <v>0.070081</v>
+        <v>0.293842</v>
       </c>
       <c r="D91" t="n">
-        <v>0.919712</v>
+        <v>0.8223</v>
       </c>
     </row>
     <row r="92">
@@ -2253,10 +2253,10 @@
         <v>41</v>
       </c>
       <c r="C92" t="n">
-        <v>0.06923899999999999</v>
+        <v>0.286519</v>
       </c>
       <c r="D92" t="n">
-        <v>0.919249</v>
+        <v>0.816991</v>
       </c>
     </row>
     <row r="93">
@@ -2269,10 +2269,10 @@
         <v>42</v>
       </c>
       <c r="C93" t="n">
-        <v>0.068964</v>
+        <v>0.293798</v>
       </c>
       <c r="D93" t="n">
-        <v>0.920161</v>
+        <v>0.821466</v>
       </c>
     </row>
     <row r="94">
@@ -2285,10 +2285,10 @@
         <v>43</v>
       </c>
       <c r="C94" t="n">
-        <v>0.068164</v>
+        <v>0.284893</v>
       </c>
       <c r="D94" t="n">
-        <v>0.919611</v>
+        <v>0.814509</v>
       </c>
     </row>
     <row r="95">
@@ -2301,10 +2301,10 @@
         <v>44</v>
       </c>
       <c r="C95" t="n">
-        <v>0.06802</v>
+        <v>0.283383</v>
       </c>
       <c r="D95" t="n">
-        <v>0.922198</v>
+        <v>0.8299260000000001</v>
       </c>
     </row>
     <row r="96">
@@ -2317,10 +2317,10 @@
         <v>45</v>
       </c>
       <c r="C96" t="n">
-        <v>0.06714100000000001</v>
+        <v>0.281285</v>
       </c>
       <c r="D96" t="n">
-        <v>0.919435</v>
+        <v>0.8241309999999999</v>
       </c>
     </row>
     <row r="97">
@@ -2333,10 +2333,10 @@
         <v>46</v>
       </c>
       <c r="C97" t="n">
-        <v>0.066597</v>
+        <v>0.293404</v>
       </c>
       <c r="D97" t="n">
-        <v>0.919809</v>
+        <v>0.829167</v>
       </c>
     </row>
     <row r="98">
@@ -2349,10 +2349,10 @@
         <v>47</v>
       </c>
       <c r="C98" t="n">
-        <v>0.06714100000000001</v>
+        <v>0.293763</v>
       </c>
       <c r="D98" t="n">
-        <v>0.921543</v>
+        <v>0.8255130000000001</v>
       </c>
     </row>
     <row r="99">
@@ -2365,10 +2365,10 @@
         <v>48</v>
       </c>
       <c r="C99" t="n">
-        <v>0.067177</v>
+        <v>0.292923</v>
       </c>
       <c r="D99" t="n">
-        <v>0.919024</v>
+        <v>0.830155</v>
       </c>
     </row>
     <row r="100">
@@ -2381,10 +2381,10 @@
         <v>49</v>
       </c>
       <c r="C100" t="n">
-        <v>0.06576799999999999</v>
+        <v>0.286627</v>
       </c>
       <c r="D100" t="n">
-        <v>0.918758</v>
+        <v>0.823203</v>
       </c>
     </row>
     <row r="101">
@@ -2397,10 +2397,10 @@
         <v>50</v>
       </c>
       <c r="C101" t="n">
-        <v>0.06697</v>
+        <v>0.285487</v>
       </c>
       <c r="D101" t="n">
-        <v>0.921225</v>
+        <v>0.826956</v>
       </c>
     </row>
     <row r="102">
@@ -2413,10 +2413,10 @@
         <v>1</v>
       </c>
       <c r="C102" t="n">
-        <v>0.353211</v>
+        <v>0.643755</v>
       </c>
       <c r="D102" t="n">
-        <v>0.809426</v>
+        <v>0.578052</v>
       </c>
     </row>
     <row r="103">
@@ -2429,10 +2429,10 @@
         <v>2</v>
       </c>
       <c r="C103" t="n">
-        <v>0.177445</v>
+        <v>0.489791</v>
       </c>
       <c r="D103" t="n">
-        <v>0.861472</v>
+        <v>0.58248</v>
       </c>
     </row>
     <row r="104">
@@ -2445,10 +2445,10 @@
         <v>3</v>
       </c>
       <c r="C104" t="n">
-        <v>0.14136</v>
+        <v>0.435015</v>
       </c>
       <c r="D104" t="n">
-        <v>0.8655659999999999</v>
+        <v>0.709378</v>
       </c>
     </row>
     <row r="105">
@@ -2461,10 +2461,10 @@
         <v>4</v>
       </c>
       <c r="C105" t="n">
-        <v>0.124244</v>
+        <v>0.409287</v>
       </c>
       <c r="D105" t="n">
-        <v>0.864857</v>
+        <v>0.7829390000000001</v>
       </c>
     </row>
     <row r="106">
@@ -2477,10 +2477,10 @@
         <v>5</v>
       </c>
       <c r="C106" t="n">
-        <v>0.118011</v>
+        <v>0.395363</v>
       </c>
       <c r="D106" t="n">
-        <v>0.884603</v>
+        <v>0.780085</v>
       </c>
     </row>
     <row r="107">
@@ -2493,10 +2493,10 @@
         <v>6</v>
       </c>
       <c r="C107" t="n">
-        <v>0.110854</v>
+        <v>0.379564</v>
       </c>
       <c r="D107" t="n">
-        <v>0.884092</v>
+        <v>0.79334</v>
       </c>
     </row>
     <row r="108">
@@ -2509,10 +2509,10 @@
         <v>7</v>
       </c>
       <c r="C108" t="n">
-        <v>0.102117</v>
+        <v>0.366282</v>
       </c>
       <c r="D108" t="n">
-        <v>0.882835</v>
+        <v>0.796377</v>
       </c>
     </row>
     <row r="109">
@@ -2525,10 +2525,10 @@
         <v>8</v>
       </c>
       <c r="C109" t="n">
-        <v>0.096641</v>
+        <v>0.351777</v>
       </c>
       <c r="D109" t="n">
-        <v>0.8951170000000001</v>
+        <v>0.813238</v>
       </c>
     </row>
     <row r="110">
@@ -2541,10 +2541,10 @@
         <v>9</v>
       </c>
       <c r="C110" t="n">
-        <v>0.094517</v>
+        <v>0.347005</v>
       </c>
       <c r="D110" t="n">
-        <v>0.894841</v>
+        <v>0.807103</v>
       </c>
     </row>
     <row r="111">
@@ -2557,10 +2557,10 @@
         <v>10</v>
       </c>
       <c r="C111" t="n">
-        <v>0.091475</v>
+        <v>0.340631</v>
       </c>
       <c r="D111" t="n">
-        <v>0.903661</v>
+        <v>0.814394</v>
       </c>
     </row>
     <row r="112">
@@ -2573,10 +2573,10 @@
         <v>11</v>
       </c>
       <c r="C112" t="n">
-        <v>0.087685</v>
+        <v>0.339053</v>
       </c>
       <c r="D112" t="n">
-        <v>0.9014760000000001</v>
+        <v>0.793306</v>
       </c>
     </row>
     <row r="113">
@@ -2589,10 +2589,10 @@
         <v>12</v>
       </c>
       <c r="C113" t="n">
-        <v>0.086868</v>
+        <v>0.333734</v>
       </c>
       <c r="D113" t="n">
-        <v>0.887096</v>
+        <v>0.819442</v>
       </c>
     </row>
     <row r="114">
@@ -2605,10 +2605,10 @@
         <v>13</v>
       </c>
       <c r="C114" t="n">
-        <v>0.085357</v>
+        <v>0.320919</v>
       </c>
       <c r="D114" t="n">
-        <v>0.914262</v>
+        <v>0.823782</v>
       </c>
     </row>
     <row r="115">
@@ -2621,10 +2621,10 @@
         <v>14</v>
       </c>
       <c r="C115" t="n">
-        <v>0.081119</v>
+        <v>0.330293</v>
       </c>
       <c r="D115" t="n">
-        <v>0.9081630000000001</v>
+        <v>0.830741</v>
       </c>
     </row>
     <row r="116">
@@ -2637,10 +2637,10 @@
         <v>15</v>
       </c>
       <c r="C116" t="n">
-        <v>0.079085</v>
+        <v>0.315664</v>
       </c>
       <c r="D116" t="n">
-        <v>0.916481</v>
+        <v>0.8371459999999999</v>
       </c>
     </row>
     <row r="117">
@@ -2653,10 +2653,10 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>0.079558</v>
+        <v>0.315042</v>
       </c>
       <c r="D117" t="n">
-        <v>0.906116</v>
+        <v>0.828955</v>
       </c>
     </row>
     <row r="118">
@@ -2669,10 +2669,10 @@
         <v>17</v>
       </c>
       <c r="C118" t="n">
-        <v>0.07786</v>
+        <v>0.31877</v>
       </c>
       <c r="D118" t="n">
-        <v>0.912653</v>
+        <v>0.833822</v>
       </c>
     </row>
     <row r="119">
@@ -2685,10 +2685,10 @@
         <v>18</v>
       </c>
       <c r="C119" t="n">
-        <v>0.075548</v>
+        <v>0.311694</v>
       </c>
       <c r="D119" t="n">
-        <v>0.911481</v>
+        <v>0.82365</v>
       </c>
     </row>
     <row r="120">
@@ -2701,10 +2701,10 @@
         <v>19</v>
       </c>
       <c r="C120" t="n">
-        <v>0.074346</v>
+        <v>0.29442</v>
       </c>
       <c r="D120" t="n">
-        <v>0.922293</v>
+        <v>0.830734</v>
       </c>
     </row>
     <row r="121">
@@ -2717,10 +2717,10 @@
         <v>20</v>
       </c>
       <c r="C121" t="n">
-        <v>0.072296</v>
+        <v>0.298743</v>
       </c>
       <c r="D121" t="n">
-        <v>0.920719</v>
+        <v>0.829605</v>
       </c>
     </row>
     <row r="122">
@@ -2733,10 +2733,10 @@
         <v>21</v>
       </c>
       <c r="C122" t="n">
-        <v>0.071618</v>
+        <v>0.29681</v>
       </c>
       <c r="D122" t="n">
-        <v>0.922713</v>
+        <v>0.835947</v>
       </c>
     </row>
     <row r="123">
@@ -2749,10 +2749,10 @@
         <v>22</v>
       </c>
       <c r="C123" t="n">
-        <v>0.06961100000000001</v>
+        <v>0.296471</v>
       </c>
       <c r="D123" t="n">
-        <v>0.914096</v>
+        <v>0.844844</v>
       </c>
     </row>
     <row r="124">
@@ -2765,10 +2765,10 @@
         <v>23</v>
       </c>
       <c r="C124" t="n">
-        <v>0.067868</v>
+        <v>0.27923</v>
       </c>
       <c r="D124" t="n">
-        <v>0.922699</v>
+        <v>0.844949</v>
       </c>
     </row>
     <row r="125">
@@ -2781,10 +2781,10 @@
         <v>24</v>
       </c>
       <c r="C125" t="n">
-        <v>0.068088</v>
+        <v>0.294797</v>
       </c>
       <c r="D125" t="n">
-        <v>0.92265</v>
+        <v>0.834095</v>
       </c>
     </row>
     <row r="126">
@@ -2797,10 +2797,10 @@
         <v>25</v>
       </c>
       <c r="C126" t="n">
-        <v>0.064919</v>
+        <v>0.271888</v>
       </c>
       <c r="D126" t="n">
-        <v>0.923036</v>
+        <v>0.847599</v>
       </c>
     </row>
     <row r="127">
@@ -2813,10 +2813,10 @@
         <v>26</v>
       </c>
       <c r="C127" t="n">
-        <v>0.064896</v>
+        <v>0.290023</v>
       </c>
       <c r="D127" t="n">
-        <v>0.931119</v>
+        <v>0.838267</v>
       </c>
     </row>
     <row r="128">
@@ -2829,10 +2829,10 @@
         <v>27</v>
       </c>
       <c r="C128" t="n">
-        <v>0.063778</v>
+        <v>0.287804</v>
       </c>
       <c r="D128" t="n">
-        <v>0.925779</v>
+        <v>0.849642</v>
       </c>
     </row>
     <row r="129">
@@ -2845,10 +2845,10 @@
         <v>28</v>
       </c>
       <c r="C129" t="n">
-        <v>0.062438</v>
+        <v>0.271184</v>
       </c>
       <c r="D129" t="n">
-        <v>0.932704</v>
+        <v>0.8518289999999999</v>
       </c>
     </row>
     <row r="130">
@@ -2861,10 +2861,10 @@
         <v>29</v>
       </c>
       <c r="C130" t="n">
-        <v>0.061226</v>
+        <v>0.282138</v>
       </c>
       <c r="D130" t="n">
-        <v>0.929484</v>
+        <v>0.851052</v>
       </c>
     </row>
     <row r="131">
@@ -2877,10 +2877,10 @@
         <v>30</v>
       </c>
       <c r="C131" t="n">
-        <v>0.060538</v>
+        <v>0.27202</v>
       </c>
       <c r="D131" t="n">
-        <v>0.930221</v>
+        <v>0.85273</v>
       </c>
     </row>
     <row r="132">
@@ -2893,10 +2893,10 @@
         <v>31</v>
       </c>
       <c r="C132" t="n">
-        <v>0.058679</v>
+        <v>0.270834</v>
       </c>
       <c r="D132" t="n">
-        <v>0.932849</v>
+        <v>0.851555</v>
       </c>
     </row>
     <row r="133">
@@ -2909,10 +2909,10 @@
         <v>32</v>
       </c>
       <c r="C133" t="n">
-        <v>0.059208</v>
+        <v>0.264771</v>
       </c>
       <c r="D133" t="n">
-        <v>0.929569</v>
+        <v>0.857916</v>
       </c>
     </row>
     <row r="134">
@@ -2925,10 +2925,10 @@
         <v>33</v>
       </c>
       <c r="C134" t="n">
-        <v>0.057974</v>
+        <v>0.270186</v>
       </c>
       <c r="D134" t="n">
-        <v>0.931747</v>
+        <v>0.857327</v>
       </c>
     </row>
     <row r="135">
@@ -2941,10 +2941,10 @@
         <v>34</v>
       </c>
       <c r="C135" t="n">
-        <v>0.056978</v>
+        <v>0.267984</v>
       </c>
       <c r="D135" t="n">
-        <v>0.933499</v>
+        <v>0.856572</v>
       </c>
     </row>
     <row r="136">
@@ -2957,10 +2957,10 @@
         <v>35</v>
       </c>
       <c r="C136" t="n">
-        <v>0.055879</v>
+        <v>0.250058</v>
       </c>
       <c r="D136" t="n">
-        <v>0.934212</v>
+        <v>0.855181</v>
       </c>
     </row>
     <row r="137">
@@ -2973,10 +2973,10 @@
         <v>36</v>
       </c>
       <c r="C137" t="n">
-        <v>0.054843</v>
+        <v>0.248112</v>
       </c>
       <c r="D137" t="n">
-        <v>0.936258</v>
+        <v>0.858978</v>
       </c>
     </row>
     <row r="138">
@@ -2989,10 +2989,10 @@
         <v>37</v>
       </c>
       <c r="C138" t="n">
-        <v>0.053618</v>
+        <v>0.246921</v>
       </c>
       <c r="D138" t="n">
-        <v>0.9372509999999999</v>
+        <v>0.8614309999999999</v>
       </c>
     </row>
     <row r="139">
@@ -3005,10 +3005,10 @@
         <v>38</v>
       </c>
       <c r="C139" t="n">
-        <v>0.053103</v>
+        <v>0.256046</v>
       </c>
       <c r="D139" t="n">
-        <v>0.936461</v>
+        <v>0.859165</v>
       </c>
     </row>
     <row r="140">
@@ -3021,10 +3021,10 @@
         <v>39</v>
       </c>
       <c r="C140" t="n">
-        <v>0.053826</v>
+        <v>0.249611</v>
       </c>
       <c r="D140" t="n">
-        <v>0.937694</v>
+        <v>0.860255</v>
       </c>
     </row>
     <row r="141">
@@ -3037,10 +3037,10 @@
         <v>40</v>
       </c>
       <c r="C141" t="n">
-        <v>0.052753</v>
+        <v>0.240923</v>
       </c>
       <c r="D141" t="n">
-        <v>0.936947</v>
+        <v>0.860455</v>
       </c>
     </row>
     <row r="142">
@@ -3053,10 +3053,10 @@
         <v>41</v>
       </c>
       <c r="C142" t="n">
-        <v>0.052162</v>
+        <v>0.256529</v>
       </c>
       <c r="D142" t="n">
-        <v>0.936958</v>
+        <v>0.861284</v>
       </c>
     </row>
     <row r="143">
@@ -3069,10 +3069,10 @@
         <v>42</v>
       </c>
       <c r="C143" t="n">
-        <v>0.051775</v>
+        <v>0.240716</v>
       </c>
       <c r="D143" t="n">
-        <v>0.938656</v>
+        <v>0.861329</v>
       </c>
     </row>
     <row r="144">
@@ -3085,10 +3085,10 @@
         <v>43</v>
       </c>
       <c r="C144" t="n">
-        <v>0.050931</v>
+        <v>0.243589</v>
       </c>
       <c r="D144" t="n">
-        <v>0.936841</v>
+        <v>0.8631259999999999</v>
       </c>
     </row>
     <row r="145">
@@ -3101,10 +3101,10 @@
         <v>44</v>
       </c>
       <c r="C145" t="n">
-        <v>0.051163</v>
+        <v>0.231694</v>
       </c>
       <c r="D145" t="n">
-        <v>0.938012</v>
+        <v>0.863181</v>
       </c>
     </row>
     <row r="146">
@@ -3117,10 +3117,10 @@
         <v>45</v>
       </c>
       <c r="C146" t="n">
-        <v>0.050424</v>
+        <v>0.240414</v>
       </c>
       <c r="D146" t="n">
-        <v>0.937837</v>
+        <v>0.864107</v>
       </c>
     </row>
     <row r="147">
@@ -3133,10 +3133,10 @@
         <v>46</v>
       </c>
       <c r="C147" t="n">
-        <v>0.050829</v>
+        <v>0.239398</v>
       </c>
       <c r="D147" t="n">
-        <v>0.93759</v>
+        <v>0.86448</v>
       </c>
     </row>
     <row r="148">
@@ -3149,10 +3149,10 @@
         <v>47</v>
       </c>
       <c r="C148" t="n">
-        <v>0.050537</v>
+        <v>0.233841</v>
       </c>
       <c r="D148" t="n">
-        <v>0.937568</v>
+        <v>0.863673</v>
       </c>
     </row>
     <row r="149">
@@ -3165,10 +3165,10 @@
         <v>48</v>
       </c>
       <c r="C149" t="n">
-        <v>0.050934</v>
+        <v>0.237698</v>
       </c>
       <c r="D149" t="n">
-        <v>0.938035</v>
+        <v>0.864185</v>
       </c>
     </row>
     <row r="150">
@@ -3181,10 +3181,10 @@
         <v>49</v>
       </c>
       <c r="C150" t="n">
-        <v>0.049333</v>
+        <v>0.235129</v>
       </c>
       <c r="D150" t="n">
-        <v>0.938356</v>
+        <v>0.863879</v>
       </c>
     </row>
     <row r="151">
@@ -3197,810 +3197,810 @@
         <v>50</v>
       </c>
       <c r="C151" t="n">
-        <v>0.049897</v>
+        <v>0.243152</v>
       </c>
       <c r="D151" t="n">
-        <v>0.938195</v>
+        <v>0.8644500000000001</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B152" t="n">
         <v>1</v>
       </c>
       <c r="C152" t="n">
-        <v>0.360537</v>
+        <v>0.618412</v>
       </c>
       <c r="D152" t="n">
-        <v>0.76301</v>
+        <v>0.538246</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B153" t="n">
         <v>2</v>
       </c>
       <c r="C153" t="n">
-        <v>0.191622</v>
+        <v>0.516195</v>
       </c>
       <c r="D153" t="n">
-        <v>0.848312</v>
+        <v>0.7045940000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B154" t="n">
         <v>3</v>
       </c>
       <c r="C154" t="n">
-        <v>0.153725</v>
+        <v>0.467387</v>
       </c>
       <c r="D154" t="n">
-        <v>0.843894</v>
+        <v>0.7437510000000001</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B155" t="n">
         <v>4</v>
       </c>
       <c r="C155" t="n">
-        <v>0.137255</v>
+        <v>0.438272</v>
       </c>
       <c r="D155" t="n">
-        <v>0.861874</v>
+        <v>0.7694839999999999</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B156" t="n">
         <v>5</v>
       </c>
       <c r="C156" t="n">
-        <v>0.121545</v>
+        <v>0.419649</v>
       </c>
       <c r="D156" t="n">
-        <v>0.891824</v>
+        <v>0.695759</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B157" t="n">
         <v>6</v>
       </c>
       <c r="C157" t="n">
-        <v>0.115285</v>
+        <v>0.419243</v>
       </c>
       <c r="D157" t="n">
-        <v>0.8707009999999999</v>
+        <v>0.775493</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B158" t="n">
         <v>7</v>
       </c>
       <c r="C158" t="n">
-        <v>0.108197</v>
+        <v>0.394835</v>
       </c>
       <c r="D158" t="n">
-        <v>0.8893489999999999</v>
+        <v>0.81136</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B159" t="n">
         <v>8</v>
       </c>
       <c r="C159" t="n">
-        <v>0.103959</v>
+        <v>0.390178</v>
       </c>
       <c r="D159" t="n">
-        <v>0.889254</v>
+        <v>0.777396</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B160" t="n">
         <v>9</v>
       </c>
       <c r="C160" t="n">
-        <v>0.09868200000000001</v>
+        <v>0.387106</v>
       </c>
       <c r="D160" t="n">
-        <v>0.89599</v>
+        <v>0.786722</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B161" t="n">
         <v>10</v>
       </c>
       <c r="C161" t="n">
-        <v>0.096971</v>
+        <v>0.372173</v>
       </c>
       <c r="D161" t="n">
-        <v>0.8927659999999999</v>
+        <v>0.816238</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B162" t="n">
         <v>11</v>
       </c>
       <c r="C162" t="n">
-        <v>0.09551</v>
+        <v>0.370856</v>
       </c>
       <c r="D162" t="n">
-        <v>0.905528</v>
+        <v>0.795328</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B163" t="n">
         <v>12</v>
       </c>
       <c r="C163" t="n">
-        <v>0.091545</v>
+        <v>0.371002</v>
       </c>
       <c r="D163" t="n">
-        <v>0.907803</v>
+        <v>0.759119</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B164" t="n">
         <v>13</v>
       </c>
       <c r="C164" t="n">
-        <v>0.088946</v>
+        <v>0.355378</v>
       </c>
       <c r="D164" t="n">
-        <v>0.891151</v>
+        <v>0.756185</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B165" t="n">
         <v>14</v>
       </c>
       <c r="C165" t="n">
-        <v>0.086213</v>
+        <v>0.360695</v>
       </c>
       <c r="D165" t="n">
-        <v>0.913358</v>
+        <v>0.774498</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B166" t="n">
         <v>15</v>
       </c>
       <c r="C166" t="n">
-        <v>0.083189</v>
+        <v>0.358524</v>
       </c>
       <c r="D166" t="n">
-        <v>0.90513</v>
+        <v>0.8272350000000001</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B167" t="n">
         <v>16</v>
       </c>
       <c r="C167" t="n">
-        <v>0.084554</v>
+        <v>0.331399</v>
       </c>
       <c r="D167" t="n">
-        <v>0.907305</v>
+        <v>0.824944</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B168" t="n">
         <v>17</v>
       </c>
       <c r="C168" t="n">
-        <v>0.08241800000000001</v>
+        <v>0.349422</v>
       </c>
       <c r="D168" t="n">
-        <v>0.898162</v>
+        <v>0.830548</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B169" t="n">
         <v>18</v>
       </c>
       <c r="C169" t="n">
-        <v>0.079193</v>
+        <v>0.331454</v>
       </c>
       <c r="D169" t="n">
-        <v>0.920884</v>
+        <v>0.821029</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B170" t="n">
         <v>19</v>
       </c>
       <c r="C170" t="n">
-        <v>0.07588300000000001</v>
+        <v>0.333031</v>
       </c>
       <c r="D170" t="n">
-        <v>0.915767</v>
+        <v>0.813839</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B171" t="n">
         <v>20</v>
       </c>
       <c r="C171" t="n">
-        <v>0.074936</v>
+        <v>0.329365</v>
       </c>
       <c r="D171" t="n">
-        <v>0.918346</v>
+        <v>0.820956</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B172" t="n">
         <v>21</v>
       </c>
       <c r="C172" t="n">
-        <v>0.0725</v>
+        <v>0.333396</v>
       </c>
       <c r="D172" t="n">
-        <v>0.923242</v>
+        <v>0.8455</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B173" t="n">
         <v>22</v>
       </c>
       <c r="C173" t="n">
-        <v>0.071841</v>
+        <v>0.30341</v>
       </c>
       <c r="D173" t="n">
-        <v>0.916127</v>
+        <v>0.841361</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B174" t="n">
         <v>23</v>
       </c>
       <c r="C174" t="n">
-        <v>0.071283</v>
+        <v>0.327037</v>
       </c>
       <c r="D174" t="n">
-        <v>0.921414</v>
+        <v>0.825215</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B175" t="n">
         <v>24</v>
       </c>
       <c r="C175" t="n">
-        <v>0.06959700000000001</v>
+        <v>0.311488</v>
       </c>
       <c r="D175" t="n">
-        <v>0.922141</v>
+        <v>0.843276</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B176" t="n">
         <v>25</v>
       </c>
       <c r="C176" t="n">
-        <v>0.06845999999999999</v>
+        <v>0.3136</v>
       </c>
       <c r="D176" t="n">
-        <v>0.921307</v>
+        <v>0.851858</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B177" t="n">
         <v>26</v>
       </c>
       <c r="C177" t="n">
-        <v>0.067132</v>
+        <v>0.311914</v>
       </c>
       <c r="D177" t="n">
-        <v>0.927691</v>
+        <v>0.843224</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B178" t="n">
         <v>27</v>
       </c>
       <c r="C178" t="n">
-        <v>0.066874</v>
+        <v>0.308717</v>
       </c>
       <c r="D178" t="n">
-        <v>0.921752</v>
+        <v>0.835226</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B179" t="n">
         <v>28</v>
       </c>
       <c r="C179" t="n">
-        <v>0.065148</v>
+        <v>0.302704</v>
       </c>
       <c r="D179" t="n">
-        <v>0.9259309999999999</v>
+        <v>0.840846</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B180" t="n">
         <v>29</v>
       </c>
       <c r="C180" t="n">
-        <v>0.06503100000000001</v>
+        <v>0.296618</v>
       </c>
       <c r="D180" t="n">
-        <v>0.927999</v>
+        <v>0.836413</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B181" t="n">
         <v>30</v>
       </c>
       <c r="C181" t="n">
-        <v>0.062152</v>
+        <v>0.294385</v>
       </c>
       <c r="D181" t="n">
-        <v>0.925786</v>
+        <v>0.841919</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B182" t="n">
         <v>31</v>
       </c>
       <c r="C182" t="n">
-        <v>0.061935</v>
+        <v>0.295965</v>
       </c>
       <c r="D182" t="n">
-        <v>0.925823</v>
+        <v>0.843697</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B183" t="n">
         <v>32</v>
       </c>
       <c r="C183" t="n">
-        <v>0.061105</v>
+        <v>0.286326</v>
       </c>
       <c r="D183" t="n">
-        <v>0.93166</v>
+        <v>0.8480839999999999</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B184" t="n">
         <v>33</v>
       </c>
       <c r="C184" t="n">
-        <v>0.060453</v>
+        <v>0.284164</v>
       </c>
       <c r="D184" t="n">
-        <v>0.927735</v>
+        <v>0.849791</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B185" t="n">
         <v>34</v>
       </c>
       <c r="C185" t="n">
-        <v>0.059267</v>
+        <v>0.281717</v>
       </c>
       <c r="D185" t="n">
-        <v>0.925735</v>
+        <v>0.852712</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B186" t="n">
         <v>35</v>
       </c>
       <c r="C186" t="n">
-        <v>0.057967</v>
+        <v>0.273417</v>
       </c>
       <c r="D186" t="n">
-        <v>0.930797</v>
+        <v>0.8510259999999999</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B187" t="n">
         <v>36</v>
       </c>
       <c r="C187" t="n">
-        <v>0.057361</v>
+        <v>0.279841</v>
       </c>
       <c r="D187" t="n">
-        <v>0.932822</v>
+        <v>0.848061</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B188" t="n">
         <v>37</v>
       </c>
       <c r="C188" t="n">
-        <v>0.056918</v>
+        <v>0.278152</v>
       </c>
       <c r="D188" t="n">
-        <v>0.932912</v>
+        <v>0.855873</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B189" t="n">
         <v>38</v>
       </c>
       <c r="C189" t="n">
-        <v>0.056391</v>
+        <v>0.269628</v>
       </c>
       <c r="D189" t="n">
-        <v>0.933121</v>
+        <v>0.852227</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B190" t="n">
         <v>39</v>
       </c>
       <c r="C190" t="n">
-        <v>0.055488</v>
+        <v>0.269068</v>
       </c>
       <c r="D190" t="n">
-        <v>0.933617</v>
+        <v>0.854221</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B191" t="n">
         <v>40</v>
       </c>
       <c r="C191" t="n">
-        <v>0.055232</v>
+        <v>0.258412</v>
       </c>
       <c r="D191" t="n">
-        <v>0.93358</v>
+        <v>0.852236</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B192" t="n">
         <v>41</v>
       </c>
       <c r="C192" t="n">
-        <v>0.054073</v>
+        <v>0.264546</v>
       </c>
       <c r="D192" t="n">
-        <v>0.934425</v>
+        <v>0.846691</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B193" t="n">
         <v>42</v>
       </c>
       <c r="C193" t="n">
-        <v>0.054132</v>
+        <v>0.259237</v>
       </c>
       <c r="D193" t="n">
-        <v>0.934874</v>
+        <v>0.853288</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B194" t="n">
         <v>43</v>
       </c>
       <c r="C194" t="n">
-        <v>0.05406</v>
+        <v>0.264723</v>
       </c>
       <c r="D194" t="n">
-        <v>0.934567</v>
+        <v>0.853019</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B195" t="n">
         <v>44</v>
       </c>
       <c r="C195" t="n">
-        <v>0.053341</v>
+        <v>0.258909</v>
       </c>
       <c r="D195" t="n">
-        <v>0.934388</v>
+        <v>0.851718</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B196" t="n">
         <v>45</v>
       </c>
       <c r="C196" t="n">
-        <v>0.052669</v>
+        <v>0.251945</v>
       </c>
       <c r="D196" t="n">
-        <v>0.935084</v>
+        <v>0.852394</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B197" t="n">
         <v>46</v>
       </c>
       <c r="C197" t="n">
-        <v>0.052628</v>
+        <v>0.270862</v>
       </c>
       <c r="D197" t="n">
-        <v>0.9351660000000001</v>
+        <v>0.852685</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B198" t="n">
         <v>47</v>
       </c>
       <c r="C198" t="n">
-        <v>0.052556</v>
+        <v>0.258594</v>
       </c>
       <c r="D198" t="n">
-        <v>0.935319</v>
+        <v>0.853436</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B199" t="n">
         <v>48</v>
       </c>
       <c r="C199" t="n">
-        <v>0.052308</v>
+        <v>0.263541</v>
       </c>
       <c r="D199" t="n">
-        <v>0.936115</v>
+        <v>0.853082</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B200" t="n">
         <v>49</v>
       </c>
       <c r="C200" t="n">
-        <v>0.051957</v>
+        <v>0.269264</v>
       </c>
       <c r="D200" t="n">
-        <v>0.935226</v>
+        <v>0.854463</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>PLWCE+Dice           (alpha=2.68)</t>
+          <t>PLWCE+Dice           (alpha=6.90)</t>
         </is>
       </c>
       <c r="B201" t="n">
         <v>50</v>
       </c>
       <c r="C201" t="n">
-        <v>0.05218</v>
+        <v>0.262198</v>
       </c>
       <c r="D201" t="n">
-        <v>0.935133</v>
+        <v>0.854969</v>
       </c>
     </row>
     <row r="202">
@@ -4013,10 +4013,10 @@
         <v>1</v>
       </c>
       <c r="C202" t="n">
-        <v>0.477626</v>
+        <v>0.610409</v>
       </c>
       <c r="D202" t="n">
-        <v>0.715403</v>
+        <v>0.6697959999999999</v>
       </c>
     </row>
     <row r="203">
@@ -4029,10 +4029,10 @@
         <v>2</v>
       </c>
       <c r="C203" t="n">
-        <v>0.227509</v>
+        <v>0.481725</v>
       </c>
       <c r="D203" t="n">
-        <v>0.835558</v>
+        <v>0.704644</v>
       </c>
     </row>
     <row r="204">
@@ -4045,10 +4045,10 @@
         <v>3</v>
       </c>
       <c r="C204" t="n">
-        <v>0.166786</v>
+        <v>0.445607</v>
       </c>
       <c r="D204" t="n">
-        <v>0.872456</v>
+        <v>0.739023</v>
       </c>
     </row>
     <row r="205">
@@ -4061,10 +4061,10 @@
         <v>4</v>
       </c>
       <c r="C205" t="n">
-        <v>0.140717</v>
+        <v>0.39767</v>
       </c>
       <c r="D205" t="n">
-        <v>0.886798</v>
+        <v>0.75426</v>
       </c>
     </row>
     <row r="206">
@@ -4077,10 +4077,10 @@
         <v>5</v>
       </c>
       <c r="C206" t="n">
-        <v>0.126632</v>
+        <v>0.387117</v>
       </c>
       <c r="D206" t="n">
-        <v>0.881827</v>
+        <v>0.754928</v>
       </c>
     </row>
     <row r="207">
@@ -4093,10 +4093,10 @@
         <v>6</v>
       </c>
       <c r="C207" t="n">
-        <v>0.114192</v>
+        <v>0.369689</v>
       </c>
       <c r="D207" t="n">
-        <v>0.87436</v>
+        <v>0.799441</v>
       </c>
     </row>
     <row r="208">
@@ -4109,10 +4109,10 @@
         <v>7</v>
       </c>
       <c r="C208" t="n">
-        <v>0.107603</v>
+        <v>0.369351</v>
       </c>
       <c r="D208" t="n">
-        <v>0.891162</v>
+        <v>0.81312</v>
       </c>
     </row>
     <row r="209">
@@ -4125,10 +4125,10 @@
         <v>8</v>
       </c>
       <c r="C209" t="n">
-        <v>0.099925</v>
+        <v>0.359098</v>
       </c>
       <c r="D209" t="n">
-        <v>0.889336</v>
+        <v>0.800777</v>
       </c>
     </row>
     <row r="210">
@@ -4141,10 +4141,10 @@
         <v>9</v>
       </c>
       <c r="C210" t="n">
-        <v>0.096316</v>
+        <v>0.344618</v>
       </c>
       <c r="D210" t="n">
-        <v>0.883088</v>
+        <v>0.787039</v>
       </c>
     </row>
     <row r="211">
@@ -4157,10 +4157,10 @@
         <v>10</v>
       </c>
       <c r="C211" t="n">
-        <v>0.092504</v>
+        <v>0.336969</v>
       </c>
       <c r="D211" t="n">
-        <v>0.892505</v>
+        <v>0.807584</v>
       </c>
     </row>
     <row r="212">
@@ -4173,10 +4173,10 @@
         <v>11</v>
       </c>
       <c r="C212" t="n">
-        <v>0.08969299999999999</v>
+        <v>0.33901</v>
       </c>
       <c r="D212" t="n">
-        <v>0.900884</v>
+        <v>0.801458</v>
       </c>
     </row>
     <row r="213">
@@ -4189,10 +4189,10 @@
         <v>12</v>
       </c>
       <c r="C213" t="n">
-        <v>0.089924</v>
+        <v>0.329806</v>
       </c>
       <c r="D213" t="n">
-        <v>0.911301</v>
+        <v>0.816539</v>
       </c>
     </row>
     <row r="214">
@@ -4205,10 +4205,10 @@
         <v>13</v>
       </c>
       <c r="C214" t="n">
-        <v>0.082297</v>
+        <v>0.330663</v>
       </c>
       <c r="D214" t="n">
-        <v>0.9081669999999999</v>
+        <v>0.814366</v>
       </c>
     </row>
     <row r="215">
@@ -4221,10 +4221,10 @@
         <v>14</v>
       </c>
       <c r="C215" t="n">
-        <v>0.080313</v>
+        <v>0.315579</v>
       </c>
       <c r="D215" t="n">
-        <v>0.90552</v>
+        <v>0.819828</v>
       </c>
     </row>
     <row r="216">
@@ -4237,10 +4237,10 @@
         <v>15</v>
       </c>
       <c r="C216" t="n">
-        <v>0.080084</v>
+        <v>0.319548</v>
       </c>
       <c r="D216" t="n">
-        <v>0.913043</v>
+        <v>0.830713</v>
       </c>
     </row>
     <row r="217">
@@ -4253,10 +4253,10 @@
         <v>16</v>
       </c>
       <c r="C217" t="n">
-        <v>0.077018</v>
+        <v>0.317407</v>
       </c>
       <c r="D217" t="n">
-        <v>0.90517</v>
+        <v>0.831512</v>
       </c>
     </row>
     <row r="218">
@@ -4269,10 +4269,10 @@
         <v>17</v>
       </c>
       <c r="C218" t="n">
-        <v>0.07549599999999999</v>
+        <v>0.312651</v>
       </c>
       <c r="D218" t="n">
-        <v>0.90908</v>
+        <v>0.831944</v>
       </c>
     </row>
     <row r="219">
@@ -4285,10 +4285,10 @@
         <v>18</v>
       </c>
       <c r="C219" t="n">
-        <v>0.076543</v>
+        <v>0.306446</v>
       </c>
       <c r="D219" t="n">
-        <v>0.914925</v>
+        <v>0.831261</v>
       </c>
     </row>
     <row r="220">
@@ -4301,10 +4301,10 @@
         <v>19</v>
       </c>
       <c r="C220" t="n">
-        <v>0.07471700000000001</v>
+        <v>0.294102</v>
       </c>
       <c r="D220" t="n">
-        <v>0.909656</v>
+        <v>0.83635</v>
       </c>
     </row>
     <row r="221">
@@ -4317,10 +4317,10 @@
         <v>20</v>
       </c>
       <c r="C221" t="n">
-        <v>0.07316599999999999</v>
+        <v>0.299562</v>
       </c>
       <c r="D221" t="n">
-        <v>0.918667</v>
+        <v>0.829125</v>
       </c>
     </row>
     <row r="222">
@@ -4333,10 +4333,10 @@
         <v>21</v>
       </c>
       <c r="C222" t="n">
-        <v>0.071729</v>
+        <v>0.296221</v>
       </c>
       <c r="D222" t="n">
-        <v>0.916333</v>
+        <v>0.837418</v>
       </c>
     </row>
     <row r="223">
@@ -4349,10 +4349,10 @@
         <v>22</v>
       </c>
       <c r="C223" t="n">
-        <v>0.06780799999999999</v>
+        <v>0.290724</v>
       </c>
       <c r="D223" t="n">
-        <v>0.9228420000000001</v>
+        <v>0.8397289999999999</v>
       </c>
     </row>
     <row r="224">
@@ -4365,10 +4365,10 @@
         <v>23</v>
       </c>
       <c r="C224" t="n">
-        <v>0.067886</v>
+        <v>0.283991</v>
       </c>
       <c r="D224" t="n">
-        <v>0.91396</v>
+        <v>0.839511</v>
       </c>
     </row>
     <row r="225">
@@ -4381,10 +4381,10 @@
         <v>24</v>
       </c>
       <c r="C225" t="n">
-        <v>0.0659</v>
+        <v>0.273001</v>
       </c>
       <c r="D225" t="n">
-        <v>0.925122</v>
+        <v>0.842126</v>
       </c>
     </row>
     <row r="226">
@@ -4397,10 +4397,10 @@
         <v>25</v>
       </c>
       <c r="C226" t="n">
-        <v>0.065873</v>
+        <v>0.28445</v>
       </c>
       <c r="D226" t="n">
-        <v>0.922779</v>
+        <v>0.842741</v>
       </c>
     </row>
     <row r="227">
@@ -4413,10 +4413,10 @@
         <v>26</v>
       </c>
       <c r="C227" t="n">
-        <v>0.065216</v>
+        <v>0.284675</v>
       </c>
       <c r="D227" t="n">
-        <v>0.927624</v>
+        <v>0.841643</v>
       </c>
     </row>
     <row r="228">
@@ -4429,10 +4429,10 @@
         <v>27</v>
       </c>
       <c r="C228" t="n">
-        <v>0.061745</v>
+        <v>0.282973</v>
       </c>
       <c r="D228" t="n">
-        <v>0.919556</v>
+        <v>0.8387019999999999</v>
       </c>
     </row>
     <row r="229">
@@ -4445,10 +4445,10 @@
         <v>28</v>
       </c>
       <c r="C229" t="n">
-        <v>0.061258</v>
+        <v>0.270122</v>
       </c>
       <c r="D229" t="n">
-        <v>0.924636</v>
+        <v>0.846267</v>
       </c>
     </row>
     <row r="230">
@@ -4461,10 +4461,10 @@
         <v>29</v>
       </c>
       <c r="C230" t="n">
-        <v>0.060576</v>
+        <v>0.271063</v>
       </c>
       <c r="D230" t="n">
-        <v>0.928994</v>
+        <v>0.850167</v>
       </c>
     </row>
     <row r="231">
@@ -4477,10 +4477,10 @@
         <v>30</v>
       </c>
       <c r="C231" t="n">
-        <v>0.05933</v>
+        <v>0.262454</v>
       </c>
       <c r="D231" t="n">
-        <v>0.927141</v>
+        <v>0.850392</v>
       </c>
     </row>
     <row r="232">
@@ -4493,10 +4493,10 @@
         <v>31</v>
       </c>
       <c r="C232" t="n">
-        <v>0.059312</v>
+        <v>0.262435</v>
       </c>
       <c r="D232" t="n">
-        <v>0.9275</v>
+        <v>0.848957</v>
       </c>
     </row>
     <row r="233">
@@ -4509,10 +4509,10 @@
         <v>32</v>
       </c>
       <c r="C233" t="n">
-        <v>0.058147</v>
+        <v>0.266434</v>
       </c>
       <c r="D233" t="n">
-        <v>0.932412</v>
+        <v>0.845388</v>
       </c>
     </row>
     <row r="234">
@@ -4525,10 +4525,10 @@
         <v>33</v>
       </c>
       <c r="C234" t="n">
-        <v>0.056795</v>
+        <v>0.257037</v>
       </c>
       <c r="D234" t="n">
-        <v>0.93121</v>
+        <v>0.847876</v>
       </c>
     </row>
     <row r="235">
@@ -4541,10 +4541,10 @@
         <v>34</v>
       </c>
       <c r="C235" t="n">
-        <v>0.056916</v>
+        <v>0.255161</v>
       </c>
       <c r="D235" t="n">
-        <v>0.930316</v>
+        <v>0.848019</v>
       </c>
     </row>
     <row r="236">
@@ -4557,10 +4557,10 @@
         <v>35</v>
       </c>
       <c r="C236" t="n">
-        <v>0.056348</v>
+        <v>0.249858</v>
       </c>
       <c r="D236" t="n">
-        <v>0.93207</v>
+        <v>0.851126</v>
       </c>
     </row>
     <row r="237">
@@ -4573,10 +4573,10 @@
         <v>36</v>
       </c>
       <c r="C237" t="n">
-        <v>0.055332</v>
+        <v>0.257974</v>
       </c>
       <c r="D237" t="n">
-        <v>0.934543</v>
+        <v>0.8473889999999999</v>
       </c>
     </row>
     <row r="238">
@@ -4589,10 +4589,10 @@
         <v>37</v>
       </c>
       <c r="C238" t="n">
-        <v>0.05463</v>
+        <v>0.254977</v>
       </c>
       <c r="D238" t="n">
-        <v>0.934899</v>
+        <v>0.849808</v>
       </c>
     </row>
     <row r="239">
@@ -4605,10 +4605,10 @@
         <v>38</v>
       </c>
       <c r="C239" t="n">
-        <v>0.053651</v>
+        <v>0.24105</v>
       </c>
       <c r="D239" t="n">
-        <v>0.935994</v>
+        <v>0.8523230000000001</v>
       </c>
     </row>
     <row r="240">
@@ -4621,10 +4621,10 @@
         <v>39</v>
       </c>
       <c r="C240" t="n">
-        <v>0.051917</v>
+        <v>0.244819</v>
       </c>
       <c r="D240" t="n">
-        <v>0.9360889999999999</v>
+        <v>0.849734</v>
       </c>
     </row>
     <row r="241">
@@ -4637,10 +4637,10 @@
         <v>40</v>
       </c>
       <c r="C241" t="n">
-        <v>0.05235</v>
+        <v>0.233615</v>
       </c>
       <c r="D241" t="n">
-        <v>0.936646</v>
+        <v>0.853592</v>
       </c>
     </row>
     <row r="242">
@@ -4653,10 +4653,10 @@
         <v>41</v>
       </c>
       <c r="C242" t="n">
-        <v>0.051874</v>
+        <v>0.241383</v>
       </c>
       <c r="D242" t="n">
-        <v>0.936769</v>
+        <v>0.853149</v>
       </c>
     </row>
     <row r="243">
@@ -4669,10 +4669,10 @@
         <v>42</v>
       </c>
       <c r="C243" t="n">
-        <v>0.051508</v>
+        <v>0.239635</v>
       </c>
       <c r="D243" t="n">
-        <v>0.937376</v>
+        <v>0.852598</v>
       </c>
     </row>
     <row r="244">
@@ -4685,10 +4685,10 @@
         <v>43</v>
       </c>
       <c r="C244" t="n">
-        <v>0.050955</v>
+        <v>0.237478</v>
       </c>
       <c r="D244" t="n">
-        <v>0.936454</v>
+        <v>0.8533809999999999</v>
       </c>
     </row>
     <row r="245">
@@ -4701,10 +4701,10 @@
         <v>44</v>
       </c>
       <c r="C245" t="n">
-        <v>0.050564</v>
+        <v>0.236929</v>
       </c>
       <c r="D245" t="n">
-        <v>0.937729</v>
+        <v>0.852252</v>
       </c>
     </row>
     <row r="246">
@@ -4717,10 +4717,10 @@
         <v>45</v>
       </c>
       <c r="C246" t="n">
-        <v>0.050284</v>
+        <v>0.236283</v>
       </c>
       <c r="D246" t="n">
-        <v>0.937304</v>
+        <v>0.851569</v>
       </c>
     </row>
     <row r="247">
@@ -4733,10 +4733,10 @@
         <v>46</v>
       </c>
       <c r="C247" t="n">
-        <v>0.050359</v>
+        <v>0.244566</v>
       </c>
       <c r="D247" t="n">
-        <v>0.93725</v>
+        <v>0.853507</v>
       </c>
     </row>
     <row r="248">
@@ -4749,10 +4749,10 @@
         <v>47</v>
       </c>
       <c r="C248" t="n">
-        <v>0.049874</v>
+        <v>0.230723</v>
       </c>
       <c r="D248" t="n">
-        <v>0.937934</v>
+        <v>0.852477</v>
       </c>
     </row>
     <row r="249">
@@ -4765,10 +4765,10 @@
         <v>48</v>
       </c>
       <c r="C249" t="n">
-        <v>0.049512</v>
+        <v>0.226269</v>
       </c>
       <c r="D249" t="n">
-        <v>0.938077</v>
+        <v>0.8543190000000001</v>
       </c>
     </row>
     <row r="250">
@@ -4781,10 +4781,10 @@
         <v>49</v>
       </c>
       <c r="C250" t="n">
-        <v>0.05024</v>
+        <v>0.23289</v>
       </c>
       <c r="D250" t="n">
-        <v>0.937925</v>
+        <v>0.853696</v>
       </c>
     </row>
     <row r="251">
@@ -4797,810 +4797,810 @@
         <v>50</v>
       </c>
       <c r="C251" t="n">
-        <v>0.049438</v>
+        <v>0.232656</v>
       </c>
       <c r="D251" t="n">
-        <v>0.937961</v>
+        <v>0.852671</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B252" t="n">
         <v>1</v>
       </c>
       <c r="C252" t="n">
-        <v>0.444655</v>
+        <v>0.424627</v>
       </c>
       <c r="D252" t="n">
-        <v>0.770566</v>
+        <v>0.576774</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B253" t="n">
         <v>2</v>
       </c>
       <c r="C253" t="n">
-        <v>0.272348</v>
+        <v>0.371986</v>
       </c>
       <c r="D253" t="n">
-        <v>0.830055</v>
+        <v>0.485594</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B254" t="n">
         <v>3</v>
       </c>
       <c r="C254" t="n">
-        <v>0.197616</v>
+        <v>0.340685</v>
       </c>
       <c r="D254" t="n">
-        <v>0.85964</v>
+        <v>0.700448</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B255" t="n">
         <v>4</v>
       </c>
       <c r="C255" t="n">
-        <v>0.150735</v>
+        <v>0.327769</v>
       </c>
       <c r="D255" t="n">
-        <v>0.8565120000000001</v>
+        <v>0.721283</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B256" t="n">
         <v>5</v>
       </c>
       <c r="C256" t="n">
-        <v>0.128505</v>
+        <v>0.306583</v>
       </c>
       <c r="D256" t="n">
-        <v>0.847791</v>
+        <v>0.739842</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B257" t="n">
         <v>6</v>
       </c>
       <c r="C257" t="n">
-        <v>0.114426</v>
+        <v>0.300427</v>
       </c>
       <c r="D257" t="n">
-        <v>0.87595</v>
+        <v>0.770714</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B258" t="n">
         <v>7</v>
       </c>
       <c r="C258" t="n">
-        <v>0.106505</v>
+        <v>0.29962</v>
       </c>
       <c r="D258" t="n">
-        <v>0.852592</v>
+        <v>0.760601</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B259" t="n">
         <v>8</v>
       </c>
       <c r="C259" t="n">
-        <v>0.099423</v>
+        <v>0.286503</v>
       </c>
       <c r="D259" t="n">
-        <v>0.879235</v>
+        <v>0.75385</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B260" t="n">
         <v>9</v>
       </c>
       <c r="C260" t="n">
-        <v>0.091977</v>
+        <v>0.277795</v>
       </c>
       <c r="D260" t="n">
-        <v>0.892333</v>
+        <v>0.779543</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B261" t="n">
         <v>10</v>
       </c>
       <c r="C261" t="n">
-        <v>0.088827</v>
+        <v>0.275972</v>
       </c>
       <c r="D261" t="n">
-        <v>0.887444</v>
+        <v>0.806897</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B262" t="n">
         <v>11</v>
       </c>
       <c r="C262" t="n">
-        <v>0.085822</v>
+        <v>0.268755</v>
       </c>
       <c r="D262" t="n">
-        <v>0.905159</v>
+        <v>0.770056</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B263" t="n">
         <v>12</v>
       </c>
       <c r="C263" t="n">
-        <v>0.082951</v>
+        <v>0.267019</v>
       </c>
       <c r="D263" t="n">
-        <v>0.903435</v>
+        <v>0.78366</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B264" t="n">
         <v>13</v>
       </c>
       <c r="C264" t="n">
-        <v>0.082996</v>
+        <v>0.264096</v>
       </c>
       <c r="D264" t="n">
-        <v>0.9094640000000001</v>
+        <v>0.798899</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B265" t="n">
         <v>14</v>
       </c>
       <c r="C265" t="n">
-        <v>0.078972</v>
+        <v>0.256525</v>
       </c>
       <c r="D265" t="n">
-        <v>0.901747</v>
+        <v>0.810348</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B266" t="n">
         <v>15</v>
       </c>
       <c r="C266" t="n">
-        <v>0.07840900000000001</v>
+        <v>0.253455</v>
       </c>
       <c r="D266" t="n">
-        <v>0.911801</v>
+        <v>0.8267679999999999</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B267" t="n">
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>0.075366</v>
+        <v>0.256925</v>
       </c>
       <c r="D267" t="n">
-        <v>0.912099</v>
+        <v>0.799218</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B268" t="n">
         <v>17</v>
       </c>
       <c r="C268" t="n">
-        <v>0.071426</v>
+        <v>0.259336</v>
       </c>
       <c r="D268" t="n">
-        <v>0.904626</v>
+        <v>0.826574</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B269" t="n">
         <v>18</v>
       </c>
       <c r="C269" t="n">
-        <v>0.07052799999999999</v>
+        <v>0.255738</v>
       </c>
       <c r="D269" t="n">
-        <v>0.916365</v>
+        <v>0.783436</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B270" t="n">
         <v>19</v>
       </c>
       <c r="C270" t="n">
-        <v>0.068449</v>
+        <v>0.242547</v>
       </c>
       <c r="D270" t="n">
-        <v>0.91491</v>
+        <v>0.813577</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B271" t="n">
         <v>20</v>
       </c>
       <c r="C271" t="n">
-        <v>0.06741900000000001</v>
+        <v>0.245924</v>
       </c>
       <c r="D271" t="n">
-        <v>0.91542</v>
+        <v>0.796187</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B272" t="n">
         <v>21</v>
       </c>
       <c r="C272" t="n">
-        <v>0.06485</v>
+        <v>0.243997</v>
       </c>
       <c r="D272" t="n">
-        <v>0.919607</v>
+        <v>0.824982</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B273" t="n">
         <v>22</v>
       </c>
       <c r="C273" t="n">
-        <v>0.064695</v>
+        <v>0.238782</v>
       </c>
       <c r="D273" t="n">
-        <v>0.915632</v>
+        <v>0.833854</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B274" t="n">
         <v>23</v>
       </c>
       <c r="C274" t="n">
-        <v>0.063401</v>
+        <v>0.234876</v>
       </c>
       <c r="D274" t="n">
-        <v>0.9167110000000001</v>
+        <v>0.832337</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B275" t="n">
         <v>24</v>
       </c>
       <c r="C275" t="n">
-        <v>0.062806</v>
+        <v>0.236094</v>
       </c>
       <c r="D275" t="n">
-        <v>0.926879</v>
+        <v>0.8216830000000001</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B276" t="n">
         <v>25</v>
       </c>
       <c r="C276" t="n">
-        <v>0.060716</v>
+        <v>0.229035</v>
       </c>
       <c r="D276" t="n">
-        <v>0.912636</v>
+        <v>0.826895</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B277" t="n">
         <v>26</v>
       </c>
       <c r="C277" t="n">
-        <v>0.059554</v>
+        <v>0.232048</v>
       </c>
       <c r="D277" t="n">
-        <v>0.919032</v>
+        <v>0.823753</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B278" t="n">
         <v>27</v>
       </c>
       <c r="C278" t="n">
-        <v>0.059435</v>
+        <v>0.223235</v>
       </c>
       <c r="D278" t="n">
-        <v>0.922207</v>
+        <v>0.825319</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B279" t="n">
         <v>28</v>
       </c>
       <c r="C279" t="n">
-        <v>0.057281</v>
+        <v>0.224588</v>
       </c>
       <c r="D279" t="n">
-        <v>0.915563</v>
+        <v>0.817997</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B280" t="n">
         <v>29</v>
       </c>
       <c r="C280" t="n">
-        <v>0.056282</v>
+        <v>0.221602</v>
       </c>
       <c r="D280" t="n">
-        <v>0.925434</v>
+        <v>0.824001</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B281" t="n">
         <v>30</v>
       </c>
       <c r="C281" t="n">
-        <v>0.055197</v>
+        <v>0.221262</v>
       </c>
       <c r="D281" t="n">
-        <v>0.926489</v>
+        <v>0.834526</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B282" t="n">
         <v>31</v>
       </c>
       <c r="C282" t="n">
-        <v>0.054284</v>
+        <v>0.214028</v>
       </c>
       <c r="D282" t="n">
-        <v>0.9292820000000001</v>
+        <v>0.836013</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B283" t="n">
         <v>32</v>
       </c>
       <c r="C283" t="n">
-        <v>0.053544</v>
+        <v>0.221739</v>
       </c>
       <c r="D283" t="n">
-        <v>0.925745</v>
+        <v>0.845961</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B284" t="n">
         <v>33</v>
       </c>
       <c r="C284" t="n">
-        <v>0.053058</v>
+        <v>0.215765</v>
       </c>
       <c r="D284" t="n">
-        <v>0.92828</v>
+        <v>0.8380570000000001</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B285" t="n">
         <v>34</v>
       </c>
       <c r="C285" t="n">
-        <v>0.052133</v>
+        <v>0.211651</v>
       </c>
       <c r="D285" t="n">
-        <v>0.930686</v>
+        <v>0.836461</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B286" t="n">
         <v>35</v>
       </c>
       <c r="C286" t="n">
-        <v>0.052286</v>
+        <v>0.202446</v>
       </c>
       <c r="D286" t="n">
-        <v>0.931653</v>
+        <v>0.850969</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B287" t="n">
         <v>36</v>
       </c>
       <c r="C287" t="n">
-        <v>0.050577</v>
+        <v>0.2135</v>
       </c>
       <c r="D287" t="n">
-        <v>0.931148</v>
+        <v>0.84911</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B288" t="n">
         <v>37</v>
       </c>
       <c r="C288" t="n">
-        <v>0.050382</v>
+        <v>0.208662</v>
       </c>
       <c r="D288" t="n">
-        <v>0.928459</v>
+        <v>0.840854</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B289" t="n">
         <v>38</v>
       </c>
       <c r="C289" t="n">
-        <v>0.050144</v>
+        <v>0.209258</v>
       </c>
       <c r="D289" t="n">
-        <v>0.9322</v>
+        <v>0.84583</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B290" t="n">
         <v>39</v>
       </c>
       <c r="C290" t="n">
-        <v>0.048571</v>
+        <v>0.196786</v>
       </c>
       <c r="D290" t="n">
-        <v>0.929895</v>
+        <v>0.848515</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B291" t="n">
         <v>40</v>
       </c>
       <c r="C291" t="n">
-        <v>0.048124</v>
+        <v>0.205621</v>
       </c>
       <c r="D291" t="n">
-        <v>0.932136</v>
+        <v>0.841288</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B292" t="n">
         <v>41</v>
       </c>
       <c r="C292" t="n">
-        <v>0.048061</v>
+        <v>0.200141</v>
       </c>
       <c r="D292" t="n">
-        <v>0.932435</v>
+        <v>0.84578</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B293" t="n">
         <v>42</v>
       </c>
       <c r="C293" t="n">
-        <v>0.048264</v>
+        <v>0.20358</v>
       </c>
       <c r="D293" t="n">
-        <v>0.933407</v>
+        <v>0.843822</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B294" t="n">
         <v>43</v>
       </c>
       <c r="C294" t="n">
-        <v>0.04705</v>
+        <v>0.193773</v>
       </c>
       <c r="D294" t="n">
-        <v>0.932845</v>
+        <v>0.84912</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B295" t="n">
         <v>44</v>
       </c>
       <c r="C295" t="n">
-        <v>0.047076</v>
+        <v>0.196339</v>
       </c>
       <c r="D295" t="n">
-        <v>0.933391</v>
+        <v>0.8481300000000001</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B296" t="n">
         <v>45</v>
       </c>
       <c r="C296" t="n">
-        <v>0.046287</v>
+        <v>0.199784</v>
       </c>
       <c r="D296" t="n">
-        <v>0.934071</v>
+        <v>0.846786</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B297" t="n">
         <v>46</v>
       </c>
       <c r="C297" t="n">
-        <v>0.046415</v>
+        <v>0.200443</v>
       </c>
       <c r="D297" t="n">
-        <v>0.934047</v>
+        <v>0.847508</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B298" t="n">
         <v>47</v>
       </c>
       <c r="C298" t="n">
-        <v>0.045823</v>
+        <v>0.203885</v>
       </c>
       <c r="D298" t="n">
-        <v>0.934148</v>
+        <v>0.848843</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B299" t="n">
         <v>48</v>
       </c>
       <c r="C299" t="n">
-        <v>0.045811</v>
+        <v>0.199434</v>
       </c>
       <c r="D299" t="n">
-        <v>0.934857</v>
+        <v>0.85122</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B300" t="n">
         <v>49</v>
       </c>
       <c r="C300" t="n">
-        <v>0.045947</v>
+        <v>0.189915</v>
       </c>
       <c r="D300" t="n">
-        <v>0.934344</v>
+        <v>0.849261</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>PLWCE+Focal+Dice     (α=4.80, γ=1.10)</t>
+          <t>PLWCE+Focal+Dice     (α=9.26, γ=1.88)</t>
         </is>
       </c>
       <c r="B301" t="n">
         <v>50</v>
       </c>
       <c r="C301" t="n">
-        <v>0.046849</v>
+        <v>0.190965</v>
       </c>
       <c r="D301" t="n">
-        <v>0.934472</v>
+        <v>0.848205</v>
       </c>
     </row>
   </sheetData>
